--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488223_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488223_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0647</v>
+        <v>8.523199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.319000000000001</v>
+        <v>9.679</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2543</v>
+        <v>-1.1558</v>
       </c>
       <c r="G2" t="n">
         <v>7.3774</v>
@@ -610,13 +610,13 @@
         <v>3.891</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.4694</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.378</v>
+        <v>-0.018</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4514</v>
       </c>
       <c r="V2" t="n">
         <v>0.5034999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0961</v>
+        <v>8.2111</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4118</v>
+        <v>7.2068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6843</v>
+        <v>1.0044</v>
       </c>
       <c r="G3" t="n">
         <v>1.5755</v>
@@ -688,13 +688,13 @@
         <v>3.3352</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1508</v>
+        <v>-0.0358</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5931</v>
+        <v>0.2018</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5576</v>
+        <v>-0.2375</v>
       </c>
       <c r="V3" t="n">
         <v>3.3362</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8114</v>
+        <v>4.982</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0492</v>
+        <v>3.343</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7621</v>
+        <v>1.639</v>
       </c>
       <c r="G4" t="n">
         <v>2.5256</v>
@@ -766,13 +766,13 @@
         <v>2.7793</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1791</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.526</v>
+        <v>-0.2322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3469</v>
+        <v>0.2238</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3144</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6391</v>
+        <v>2.7982</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3743</v>
+        <v>3.755</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7351</v>
+        <v>-0.9567</v>
       </c>
       <c r="G5" t="n">
         <v>2.1113</v>
@@ -844,13 +844,13 @@
         <v>2.7793</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0063</v>
+        <v>0.1654</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9613</v>
+        <v>0.342</v>
       </c>
       <c r="U5" t="n">
-        <v>0.045</v>
+        <v>-0.1766</v>
       </c>
       <c r="V5" t="n">
         <v>1.448</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6098</v>
+        <v>0.6591</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6098</v>
+        <v>0.6591</v>
       </c>
       <c r="G8" t="n">
         <v>0.3917</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4628</v>
+        <v>-0.3402</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0209</v>
+        <v>-0.923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5581</v>
+        <v>0.5827</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5197000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2024</v>
+        <v>-0.0799</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
         <v>0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5462</v>
+        <v>-0.8094</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2442</v>
+        <v>-0.5812</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.302</v>
+        <v>-0.2282</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4736</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6685</v>
+        <v>0.4054</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6193</v>
+        <v>0.2823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0808</v>
+        <v>-2.1919</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.087</v>
+        <v>-2.1734</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0062</v>
+        <v>-0.0184</v>
       </c>
       <c r="G11" t="n">
         <v>0.1943</v>
@@ -1312,13 +1312,13 @@
         <v>2.594</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4081</v>
+        <v>-0.5192</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5014</v>
+        <v>-0.526</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7553</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5191</v>
+        <v>-2.7779</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7671</v>
+        <v>-2.8535</v>
       </c>
       <c r="F12" t="n">
-        <v>0.248</v>
+        <v>0.0756</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9579</v>
@@ -1390,13 +1390,13 @@
         <v>2.9646</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0266</v>
+        <v>-0.2854</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.092</v>
+        <v>-0.1784</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0654</v>
+        <v>-0.107</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5727</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7628</v>
+        <v>-7.3842</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0591</v>
+        <v>-4.6559</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7037</v>
+        <v>-2.7283</v>
       </c>
       <c r="G13" t="n">
         <v>-5.73</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8334</v>
+        <v>-0.4548</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4501</v>
+        <v>-0.0469</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3833</v>
+        <v>-0.4079</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3847</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.0376</v>
+        <v>13.8582</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1642</v>
+        <v>14.985</v>
       </c>
       <c r="F14" t="n">
         <v>-1.1266</v>
@@ -1546,13 +1546,13 @@
         <v>20.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0207</v>
+        <v>-1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5841999999999999</v>
+        <v>0.2366000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4365</v>
+        <v>-1.4364</v>
       </c>
       <c r="V14" t="n">
         <v>1.8906</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3569</v>
+        <v>4.5995</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2682</v>
+        <v>5.2804</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9113</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6145</v>
+        <v>2.5224</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3653</v>
+        <v>2.9108</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7508</v>
+        <v>-0.3884</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6339</v>
+        <v>4.9841</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8044</v>
+        <v>3.4911</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8294</v>
+        <v>1.493</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.0194</v>
+        <v>-2.4617</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4391</v>
+        <v>-0.5803</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5803</v>
+        <v>-1.8814</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3352</v>
+        <v>-1.1117</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2078</v>
+        <v>0.7632</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5084</v>
+        <v>0.4648</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6993</v>
+        <v>0.2984</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8316</v>
+        <v>0.9433</v>
       </c>
       <c r="W15" t="n">
-        <v>3.461</v>
+        <v>0.9433</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0114</v>
+        <v>3.5145</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1825</v>
+        <v>5.4847</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1711</v>
+        <v>-1.9702</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5224</v>
+        <v>0.6145</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9108</v>
+        <v>2.3653</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3884</v>
+        <v>-1.7508</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9841</v>
+        <v>4.6339</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4911</v>
+        <v>3.8044</v>
       </c>
       <c r="L16" t="n">
-        <v>1.493</v>
+        <v>0.8294</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4617</v>
+        <v>-4.0194</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5803</v>
+        <v>-1.4391</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8814</v>
+        <v>-2.5803</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1117</v>
+        <v>-3.3352</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1751</v>
+        <v>1.3654</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3669</v>
+        <v>0.725</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1918</v>
+        <v>0.6404</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9433</v>
+        <v>2.8316</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9433</v>
+        <v>3.461</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4891</v>
+        <v>2.5543</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4716</v>
+        <v>3.2757</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9825</v>
+        <v>-0.7214</v>
       </c>
       <c r="G17" t="n">
         <v>2.2155</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0883</v>
+        <v>0.1536</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2699</v>
+        <v>0.074</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1816</v>
+        <v>0.0796</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.778</v>
+        <v>-0.5827</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.493</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0897</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9624</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4449</v>
+        <v>-0.2496</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2116</v>
+        <v>0.1131</v>
       </c>
       <c r="V20" t="n">
         <v>1.2589</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5147</v>
+        <v>-1.0933</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1233</v>
+        <v>-0.1823</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3914</v>
+        <v>-0.911</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6787</v>
+        <v>-1.86</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3273</v>
+        <v>-0.7695</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.006</v>
+        <v>-1.0906</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1503</v>
+        <v>0.7846</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1503</v>
+        <v>0.6696</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.829</v>
+        <v>-2.6447</v>
       </c>
       <c r="N21" t="n">
-        <v>0.177</v>
+        <v>-1.4391</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.006</v>
+        <v>-1.2056</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0594</v>
+        <v>0.8223</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2736</v>
+        <v>0.4418</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2141</v>
+        <v>0.3805</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8883</v>
+        <v>0.315</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8883</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7975</v>
+        <v>-1.3921</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7741</v>
+        <v>-0.0253</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0234</v>
+        <v>-1.3668</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5749</v>
+        <v>-0.6787</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1926</v>
+        <v>0.3273</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3823</v>
+        <v>-1.006</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.1503</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5918</v>
+        <v>0.1503</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2911</v>
+        <v>-0.829</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7844</v>
+        <v>0.177</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5067</v>
+        <v>-1.006</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1117</v>
+        <v>1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5191</v>
+        <v>0.0631</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2896</v>
+        <v>-0.1756</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2295</v>
+        <v>0.2388</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.63</v>
+        <v>-1.8883</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9266</v>
+        <v>-2.4921</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4761</v>
+        <v>-2.5575</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4505</v>
+        <v>0.0654</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.86</v>
+        <v>-1.5749</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7695</v>
+        <v>-1.1926</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0906</v>
+        <v>-0.3823</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7846</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6696</v>
+        <v>0.5918</v>
       </c>
       <c r="L23" t="n">
-        <v>0.115</v>
+        <v>0.1244</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6447</v>
+        <v>-2.2911</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4391</v>
+        <v>-1.7844</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2056</v>
+        <v>-0.5067</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3706</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0382</v>
+        <v>-3.1499</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0109</v>
+        <v>0.8245</v>
       </c>
       <c r="T23" t="n">
-        <v>0.148</v>
+        <v>0.5061</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1589</v>
+        <v>0.3183</v>
       </c>
       <c r="V23" t="n">
-        <v>0.315</v>
+        <v>-0.63</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3456</v>
+        <v>-3.0708</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6975</v>
+        <v>-1.1099</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6481</v>
+        <v>-1.9609</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3237</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.763</v>
+        <v>0.5117</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.286</v>
+        <v>0.3016</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.477</v>
+        <v>0.2101</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1391</v>
+        <v>-6.7469</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5974</v>
+        <v>-3.3036</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.5417</v>
+        <v>-3.4432</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5395</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5996</v>
+        <v>-0.2074</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6019</v>
+        <v>-0.3081</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0022</v>
+        <v>0.1007</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1471</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.281700000000001</v>
+        <v>-8.2577</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.2288</v>
+        <v>-7.1309</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0529</v>
+        <v>-1.1268</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9842</v>
@@ -2482,13 +2482,13 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0915</v>
+        <v>-0.0675</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2368</v>
+        <v>0.1629</v>
       </c>
       <c r="V26" t="n">
         <v>-0.315</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.0375</v>
+        <v>-11.079</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1266</v>
+        <v>1.126600000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.1641</v>
+        <v>-12.2055</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.6827</v>
+        <v>-6.682699999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8852</v>
+        <v>-0.8852000000000004</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.7976</v>
+        <v>-5.797599999999999</v>
       </c>
       <c r="J27" t="n">
         <v>14.0947</v>
@@ -2539,7 +2539,7 @@
         <v>8.834699999999996</v>
       </c>
       <c r="L27" t="n">
-        <v>5.260000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="M27" t="n">
         <v>-20.7776</v>
@@ -2560,19 +2560,19 @@
         <v>13.8966</v>
       </c>
       <c r="S27" t="n">
-        <v>2.021</v>
+        <v>3.9793</v>
       </c>
       <c r="T27" t="n">
         <v>1.4364</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5842000000000001</v>
+        <v>2.5428</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.890500000000001</v>
+        <v>-1.8905</v>
       </c>
       <c r="W27" t="n">
-        <v>5.976999999999999</v>
+        <v>5.977</v>
       </c>
       <c r="X27" t="n">
         <v>-7.8675</v>
